--- a/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
+++ b/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/trees/RNA3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854DB035-F1CD-D44C-BAA3-3366F81C7E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE98457-C604-9649-96FE-E97289C308FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40380" yWindow="500" windowWidth="28260" windowHeight="16880" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
+    <workbookView xWindow="34680" yWindow="500" windowWidth="28260" windowHeight="21100" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="412">
   <si>
     <t>D_mel_USA_2020_mel-20-TD-3_Galbut_virus_RNA3_Complete_CDS_1</t>
   </si>
@@ -969,6 +969,309 @@
   </si>
   <si>
     <t>PV185894</t>
+  </si>
+  <si>
+    <t>sample_id</t>
+  </si>
+  <si>
+    <t>mel-21-MDS-9</t>
+  </si>
+  <si>
+    <t>500-F-11</t>
+  </si>
+  <si>
+    <t>500-F-21</t>
+  </si>
+  <si>
+    <t>500-F-67</t>
+  </si>
+  <si>
+    <t>500-M-16</t>
+  </si>
+  <si>
+    <t>500-M-17</t>
+  </si>
+  <si>
+    <t>500-M-54</t>
+  </si>
+  <si>
+    <t>500-M-57</t>
+  </si>
+  <si>
+    <t>500-M-61-2</t>
+  </si>
+  <si>
+    <t>500-M-61</t>
+  </si>
+  <si>
+    <t>500-M-65-2</t>
+  </si>
+  <si>
+    <t>500-M-65</t>
+  </si>
+  <si>
+    <t>500-M-71-2</t>
+  </si>
+  <si>
+    <t>500-M-83</t>
+  </si>
+  <si>
+    <t>500-M-84</t>
+  </si>
+  <si>
+    <t>500-M-F10</t>
+  </si>
+  <si>
+    <t>500-M-F11</t>
+  </si>
+  <si>
+    <t>500-M-G2</t>
+  </si>
+  <si>
+    <t>1020-B6</t>
+  </si>
+  <si>
+    <t>1020-C2</t>
+  </si>
+  <si>
+    <t>1020-D1</t>
+  </si>
+  <si>
+    <t>1020-D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1020-F1 </t>
+  </si>
+  <si>
+    <t>1020-F6</t>
+  </si>
+  <si>
+    <t>1020-F-31</t>
+  </si>
+  <si>
+    <t>1020-F-36</t>
+  </si>
+  <si>
+    <t>1020-F-44</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D4</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D11</t>
+  </si>
+  <si>
+    <t>1020-G3</t>
+  </si>
+  <si>
+    <t>1020-M-8</t>
+  </si>
+  <si>
+    <t>1020-M-19</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A5</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A7</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A10</t>
+  </si>
+  <si>
+    <t>1428-F-8</t>
+  </si>
+  <si>
+    <t>1428-F-21</t>
+  </si>
+  <si>
+    <t>1428-M-4</t>
+  </si>
+  <si>
+    <t>1428-M-6</t>
+  </si>
+  <si>
+    <t>1428-M-21</t>
+  </si>
+  <si>
+    <t>1428-M-42</t>
+  </si>
+  <si>
+    <t>Adobe-B4</t>
+  </si>
+  <si>
+    <t>Adobe-B6</t>
+  </si>
+  <si>
+    <t>Adobe-B8</t>
+  </si>
+  <si>
+    <t>Adobe-C2</t>
+  </si>
+  <si>
+    <t>Briarwood-D9</t>
+  </si>
+  <si>
+    <t>CVID-0825-B1</t>
+  </si>
+  <si>
+    <t>CVID-0825-C10</t>
+  </si>
+  <si>
+    <t>CVID-0911-F4</t>
+  </si>
+  <si>
+    <t>CVID-1006-G6</t>
+  </si>
+  <si>
+    <t>CVID-1006-G7</t>
+  </si>
+  <si>
+    <t>CVID-1006-H2</t>
+  </si>
+  <si>
+    <t>CVID-1006-H3</t>
+  </si>
+  <si>
+    <t>James-A4</t>
+  </si>
+  <si>
+    <t>James-A5</t>
+  </si>
+  <si>
+    <t>ME-F-1</t>
+  </si>
+  <si>
+    <t>ME-F-2</t>
+  </si>
+  <si>
+    <t>ME-F-3</t>
+  </si>
+  <si>
+    <t>ME-F-9</t>
+  </si>
+  <si>
+    <t>ME-M-1</t>
+  </si>
+  <si>
+    <t>ME-M-2</t>
+  </si>
+  <si>
+    <t>ME-M-4</t>
+  </si>
+  <si>
+    <t>ME-M-6</t>
+  </si>
+  <si>
+    <t>ME-M-10</t>
+  </si>
+  <si>
+    <t>ME-M-11</t>
+  </si>
+  <si>
+    <t>ME-M-14</t>
+  </si>
+  <si>
+    <t>ME-M-17</t>
+  </si>
+  <si>
+    <t>ME-M-18</t>
+  </si>
+  <si>
+    <t>ME-M-19</t>
+  </si>
+  <si>
+    <t>ME-M-20</t>
+  </si>
+  <si>
+    <t>Myrtle-D5</t>
+  </si>
+  <si>
+    <t>Myrtle-D11</t>
+  </si>
+  <si>
+    <t>Myrtle-E9</t>
+  </si>
+  <si>
+    <t>OH-M-5</t>
+  </si>
+  <si>
+    <t>Peach-8-F7</t>
+  </si>
+  <si>
+    <t>Peach-9-F8</t>
+  </si>
+  <si>
+    <t>Peach-10-F10</t>
+  </si>
+  <si>
+    <t>Penn-F-1</t>
+  </si>
+  <si>
+    <t>Penn-F-2</t>
+  </si>
+  <si>
+    <t>Penn-F-3</t>
+  </si>
+  <si>
+    <t>Penn-F-9</t>
+  </si>
+  <si>
+    <t>Penn-F-12</t>
+  </si>
+  <si>
+    <t>Penn-M-8</t>
+  </si>
+  <si>
+    <t>Penn-M-10</t>
+  </si>
+  <si>
+    <t>Penn-M-11</t>
+  </si>
+  <si>
+    <t>Penn-M-14</t>
+  </si>
+  <si>
+    <t>Penn-M-15</t>
+  </si>
+  <si>
+    <t>mel-20-TD-3</t>
+  </si>
+  <si>
+    <t>sim-20-TD-4</t>
+  </si>
+  <si>
+    <t>500-F-41</t>
+  </si>
+  <si>
+    <t>500-M-60</t>
+  </si>
+  <si>
+    <t>1020-A7</t>
+  </si>
+  <si>
+    <t>1020-F-40</t>
+  </si>
+  <si>
+    <t>1428-M-3</t>
+  </si>
+  <si>
+    <t>ME-M-7</t>
+  </si>
+  <si>
+    <t>ME-M-8</t>
+  </si>
+  <si>
+    <t>Peach-13-H7</t>
+  </si>
+  <si>
+    <t>Penn-F-4</t>
+  </si>
+  <si>
+    <t>Penn-M-2</t>
+  </si>
+  <si>
+    <t>ME-M-3</t>
   </si>
 </sst>
 </file>
@@ -1340,14 +1643,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFA89E3-95EE-5B4C-BA29-97DEEB829153}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="63" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -1363,8 +1667,11 @@
       <c r="E1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1380,8 +1687,11 @@
       <c r="E2" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1397,8 +1707,11 @@
       <c r="E3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1414,8 +1727,11 @@
       <c r="E4" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1431,8 +1747,11 @@
       <c r="E5" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1448,8 +1767,11 @@
       <c r="E6" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1465,8 +1787,11 @@
       <c r="E7" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1482,8 +1807,11 @@
       <c r="E8" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1499,8 +1827,11 @@
       <c r="E9" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1516,8 +1847,11 @@
       <c r="E10" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1533,8 +1867,11 @@
       <c r="E11" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1550,8 +1887,11 @@
       <c r="E12" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1567,8 +1907,11 @@
       <c r="E13" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1584,8 +1927,11 @@
       <c r="E14" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1601,8 +1947,11 @@
       <c r="E15" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1618,8 +1967,11 @@
       <c r="E16" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1635,8 +1987,11 @@
       <c r="E17" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1652,8 +2007,11 @@
       <c r="E18" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1669,8 +2027,11 @@
       <c r="E19" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1686,8 +2047,11 @@
       <c r="E20" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1703,8 +2067,11 @@
       <c r="E21" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1720,8 +2087,11 @@
       <c r="E22" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -1737,8 +2107,11 @@
       <c r="E23" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1754,8 +2127,11 @@
       <c r="E24" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1771,8 +2147,11 @@
       <c r="E25" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1788,8 +2167,11 @@
       <c r="E26" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1805,8 +2187,11 @@
       <c r="E27" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1822,8 +2207,11 @@
       <c r="E28" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1839,8 +2227,11 @@
       <c r="E29" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -1856,8 +2247,11 @@
       <c r="E30" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1873,8 +2267,11 @@
       <c r="E31" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1890,8 +2287,11 @@
       <c r="E32" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1907,8 +2307,11 @@
       <c r="E33" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -1924,8 +2327,11 @@
       <c r="E34" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -1941,8 +2347,11 @@
       <c r="E35" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1958,8 +2367,11 @@
       <c r="E36" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -1975,8 +2387,11 @@
       <c r="E37" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1992,8 +2407,11 @@
       <c r="E38" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2009,8 +2427,11 @@
       <c r="E39" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -2026,8 +2447,11 @@
       <c r="E40" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>78</v>
       </c>
@@ -2043,8 +2467,11 @@
       <c r="E41" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2060,8 +2487,11 @@
       <c r="E42" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F42" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2077,8 +2507,11 @@
       <c r="E43" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -2094,8 +2527,11 @@
       <c r="E44" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -2111,8 +2547,11 @@
       <c r="E45" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -2128,8 +2567,11 @@
       <c r="E46" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -2145,8 +2587,11 @@
       <c r="E47" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -2162,8 +2607,11 @@
       <c r="E48" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2179,8 +2627,11 @@
       <c r="E49" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -2196,8 +2647,11 @@
       <c r="E50" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -2213,8 +2667,11 @@
       <c r="E51" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F51" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -2230,8 +2687,11 @@
       <c r="E52" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F52" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -2247,8 +2707,11 @@
       <c r="E53" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2264,8 +2727,11 @@
       <c r="E54" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -2281,8 +2747,11 @@
       <c r="E55" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2298,8 +2767,11 @@
       <c r="E56" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F56" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2315,8 +2787,11 @@
       <c r="E57" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -2332,8 +2807,11 @@
       <c r="E58" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F58" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -2349,8 +2827,11 @@
       <c r="E59" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2366,8 +2847,11 @@
       <c r="E60" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2383,8 +2867,11 @@
       <c r="E61" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>120</v>
       </c>
@@ -2400,8 +2887,11 @@
       <c r="E62" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2417,8 +2907,11 @@
       <c r="E63" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2434,8 +2927,11 @@
       <c r="E64" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -2451,8 +2947,11 @@
       <c r="E65" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -2468,8 +2967,11 @@
       <c r="E66" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F66" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -2485,8 +2987,11 @@
       <c r="E67" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -2502,8 +3007,11 @@
       <c r="E68" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F68" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -2519,8 +3027,11 @@
       <c r="E69" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -2536,8 +3047,11 @@
       <c r="E70" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F70" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>138</v>
       </c>
@@ -2553,8 +3067,11 @@
       <c r="E71" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F71" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>140</v>
       </c>
@@ -2570,8 +3087,11 @@
       <c r="E72" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -2587,8 +3107,11 @@
       <c r="E73" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F73" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>144</v>
       </c>
@@ -2604,8 +3127,11 @@
       <c r="E74" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F74" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>146</v>
       </c>
@@ -2621,8 +3147,11 @@
       <c r="E75" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F75" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>148</v>
       </c>
@@ -2638,8 +3167,11 @@
       <c r="E76" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>150</v>
       </c>
@@ -2655,8 +3187,11 @@
       <c r="E77" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -2672,8 +3207,11 @@
       <c r="E78" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2689,8 +3227,11 @@
       <c r="E79" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F79" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>156</v>
       </c>
@@ -2706,8 +3247,11 @@
       <c r="E80" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F80" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>158</v>
       </c>
@@ -2723,8 +3267,11 @@
       <c r="E81" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F81" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>160</v>
       </c>
@@ -2740,8 +3287,11 @@
       <c r="E82" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F82" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -2757,8 +3307,11 @@
       <c r="E83" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F83" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -2774,8 +3327,11 @@
       <c r="E84" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F84" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -2791,8 +3347,11 @@
       <c r="E85" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F85" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2808,8 +3367,11 @@
       <c r="E86" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -2825,8 +3387,11 @@
       <c r="E87" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F87" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>172</v>
       </c>
@@ -2842,8 +3407,11 @@
       <c r="E88" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F88" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>174</v>
       </c>
@@ -2859,8 +3427,11 @@
       <c r="E89" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F89" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>176</v>
       </c>
@@ -2876,8 +3447,11 @@
       <c r="E90" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F90" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -2893,8 +3467,11 @@
       <c r="E91" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F91" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>180</v>
       </c>
@@ -2910,8 +3487,11 @@
       <c r="E92" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F92" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>182</v>
       </c>
@@ -2927,8 +3507,11 @@
       <c r="E93" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F93" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>184</v>
       </c>
@@ -2944,8 +3527,11 @@
       <c r="E94" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F94" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -2961,8 +3547,11 @@
       <c r="E95" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F95" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -2978,8 +3567,11 @@
       <c r="E96" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F96" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -2995,8 +3587,11 @@
       <c r="E97" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F97" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -3012,8 +3607,11 @@
       <c r="E98" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F98" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>194</v>
       </c>
@@ -3029,8 +3627,11 @@
       <c r="E99" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F99" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>196</v>
       </c>
@@ -3046,8 +3647,11 @@
       <c r="E100" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F100" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>198</v>
       </c>
@@ -3063,8 +3667,11 @@
       <c r="E101" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>200</v>
       </c>
@@ -3080,8 +3687,11 @@
       <c r="E102" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F102" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>202</v>
       </c>
@@ -3097,8 +3707,11 @@
       <c r="E103" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F103" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>204</v>
       </c>
@@ -3114,8 +3727,11 @@
       <c r="E104" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F104" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>206</v>
       </c>
@@ -3131,8 +3747,11 @@
       <c r="E105" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F105" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>208</v>
       </c>
@@ -3148,8 +3767,11 @@
       <c r="E106" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F106" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -3165,8 +3787,11 @@
       <c r="E107" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F107" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>212</v>
       </c>
@@ -3182,8 +3807,11 @@
       <c r="E108" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F108" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>214</v>
       </c>
@@ -3199,8 +3827,11 @@
       <c r="E109" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F109" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>216</v>
       </c>
@@ -3216,8 +3847,11 @@
       <c r="E110" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F110" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -3233,8 +3867,11 @@
       <c r="E111" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F111" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>220</v>
       </c>
@@ -3250,8 +3887,11 @@
       <c r="E112" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F112" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>222</v>
       </c>
@@ -3267,8 +3907,11 @@
       <c r="E113" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F113" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
         <v>224</v>
       </c>
@@ -3282,7 +3925,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
         <v>225</v>
       </c>
@@ -3296,7 +3939,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
         <v>226</v>
       </c>
@@ -3310,7 +3953,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
         <v>227</v>
       </c>
@@ -3324,7 +3967,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
         <v>228</v>
       </c>
@@ -3338,7 +3981,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
         <v>229</v>
       </c>
@@ -3352,7 +3995,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
         <v>230</v>
       </c>
@@ -3366,7 +4009,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
         <v>231</v>
       </c>
@@ -3380,7 +4023,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
         <v>232</v>
       </c>
@@ -3394,7 +4037,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
         <v>233</v>
       </c>
@@ -3408,7 +4051,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
         <v>234</v>
       </c>
@@ -3422,7 +4065,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
         <v>235</v>
       </c>
@@ -3436,7 +4079,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
         <v>236</v>
       </c>
@@ -3450,7 +4093,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
         <v>237</v>
       </c>
@@ -3464,7 +4107,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
         <v>238</v>
       </c>

--- a/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
+++ b/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/trees/RNA3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdstengl/Google_Drive/Projects/Galbut_virus/Diverse_Collections/DiverseCollections/analyses/trees/RNA3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854DB035-F1CD-D44C-BAA3-3366F81C7E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78439F6-3983-2548-B757-B2F49E8EC239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40380" yWindow="500" windowWidth="28260" windowHeight="16880" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="310">
   <si>
     <t>D_mel_USA_2020_mel-20-TD-3_Galbut_virus_RNA3_Complete_CDS_1</t>
   </si>
@@ -900,9 +900,6 @@
   </si>
   <si>
     <t>Ohio</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>Pennsylvania</t>
@@ -1378,7 +1375,7 @@
         <v>2020</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1395,7 +1392,7 @@
         <v>2020</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1412,7 +1409,7 @@
         <v>2020</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1429,7 +1426,7 @@
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1446,7 +1443,7 @@
         <v>2021</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1463,7 +1460,7 @@
         <v>2023</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1480,7 +1477,7 @@
         <v>2023</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1497,7 +1494,7 @@
         <v>2023</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1514,7 +1511,7 @@
         <v>2023</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1531,7 +1528,7 @@
         <v>2023</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1548,7 +1545,7 @@
         <v>2023</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1565,7 +1562,7 @@
         <v>2023</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1582,7 +1579,7 @@
         <v>2023</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1599,7 +1596,7 @@
         <v>2023</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1616,7 +1613,7 @@
         <v>2023</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1633,7 +1630,7 @@
         <v>2023</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1650,7 +1647,7 @@
         <v>2023</v>
       </c>
       <c r="E18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1667,7 +1664,7 @@
         <v>2023</v>
       </c>
       <c r="E19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1684,7 +1681,7 @@
         <v>2023</v>
       </c>
       <c r="E20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1701,7 +1698,7 @@
         <v>2023</v>
       </c>
       <c r="E21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1718,7 +1715,7 @@
         <v>2023</v>
       </c>
       <c r="E22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1735,7 +1732,7 @@
         <v>2023</v>
       </c>
       <c r="E23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1752,7 +1749,7 @@
         <v>2023</v>
       </c>
       <c r="E24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1769,7 +1766,7 @@
         <v>2023</v>
       </c>
       <c r="E25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1786,7 +1783,7 @@
         <v>2023</v>
       </c>
       <c r="E26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1803,7 +1800,7 @@
         <v>2023</v>
       </c>
       <c r="E27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1820,7 +1817,7 @@
         <v>2023</v>
       </c>
       <c r="E28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1837,7 +1834,7 @@
         <v>2023</v>
       </c>
       <c r="E29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1854,7 +1851,7 @@
         <v>2023</v>
       </c>
       <c r="E30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1871,7 +1868,7 @@
         <v>2023</v>
       </c>
       <c r="E31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1888,7 +1885,7 @@
         <v>2023</v>
       </c>
       <c r="E32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1905,7 +1902,7 @@
         <v>2023</v>
       </c>
       <c r="E33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1922,7 +1919,7 @@
         <v>2023</v>
       </c>
       <c r="E34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1939,7 +1936,7 @@
         <v>2023</v>
       </c>
       <c r="E35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1956,7 +1953,7 @@
         <v>2023</v>
       </c>
       <c r="E36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1973,7 +1970,7 @@
         <v>2023</v>
       </c>
       <c r="E37" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1990,7 +1987,7 @@
         <v>2023</v>
       </c>
       <c r="E38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -2007,7 +2004,7 @@
         <v>2023</v>
       </c>
       <c r="E39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -2024,7 +2021,7 @@
         <v>2023</v>
       </c>
       <c r="E40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -2041,7 +2038,7 @@
         <v>2023</v>
       </c>
       <c r="E41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -2058,7 +2055,7 @@
         <v>2023</v>
       </c>
       <c r="E42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -2075,7 +2072,7 @@
         <v>2023</v>
       </c>
       <c r="E43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -2092,7 +2089,7 @@
         <v>2023</v>
       </c>
       <c r="E44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -2109,7 +2106,7 @@
         <v>2023</v>
       </c>
       <c r="E45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -2126,7 +2123,7 @@
         <v>2023</v>
       </c>
       <c r="E46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -2143,7 +2140,7 @@
         <v>2023</v>
       </c>
       <c r="E47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -2160,7 +2157,7 @@
         <v>2023</v>
       </c>
       <c r="E48" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -2177,7 +2174,7 @@
         <v>2023</v>
       </c>
       <c r="E49" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -2194,7 +2191,7 @@
         <v>2023</v>
       </c>
       <c r="E50" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -2211,7 +2208,7 @@
         <v>2023</v>
       </c>
       <c r="E51" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -2228,7 +2225,7 @@
         <v>2023</v>
       </c>
       <c r="E52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -2245,7 +2242,7 @@
         <v>2023</v>
       </c>
       <c r="E53" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -2262,7 +2259,7 @@
         <v>2023</v>
       </c>
       <c r="E54" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -2279,7 +2276,7 @@
         <v>2023</v>
       </c>
       <c r="E55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -2296,7 +2293,7 @@
         <v>2023</v>
       </c>
       <c r="E56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -2313,7 +2310,7 @@
         <v>2023</v>
       </c>
       <c r="E57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -2330,7 +2327,7 @@
         <v>2023</v>
       </c>
       <c r="E58" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -2347,7 +2344,7 @@
         <v>2023</v>
       </c>
       <c r="E59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -2364,7 +2361,7 @@
         <v>2023</v>
       </c>
       <c r="E60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -2381,7 +2378,7 @@
         <v>2023</v>
       </c>
       <c r="E61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -2398,7 +2395,7 @@
         <v>2023</v>
       </c>
       <c r="E62" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -2415,7 +2412,7 @@
         <v>2023</v>
       </c>
       <c r="E63" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -2432,7 +2429,7 @@
         <v>2023</v>
       </c>
       <c r="E64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -2449,7 +2446,7 @@
         <v>2023</v>
       </c>
       <c r="E65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -2466,7 +2463,7 @@
         <v>2023</v>
       </c>
       <c r="E66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -2483,7 +2480,7 @@
         <v>2023</v>
       </c>
       <c r="E67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -2500,7 +2497,7 @@
         <v>2023</v>
       </c>
       <c r="E68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -2517,7 +2514,7 @@
         <v>2023</v>
       </c>
       <c r="E69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -2534,7 +2531,7 @@
         <v>2023</v>
       </c>
       <c r="E70" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -2551,7 +2548,7 @@
         <v>2023</v>
       </c>
       <c r="E71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -2568,7 +2565,7 @@
         <v>2023</v>
       </c>
       <c r="E72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -2585,7 +2582,7 @@
         <v>2023</v>
       </c>
       <c r="E73" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -2602,7 +2599,7 @@
         <v>2023</v>
       </c>
       <c r="E74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -2619,7 +2616,7 @@
         <v>2023</v>
       </c>
       <c r="E75" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -2636,7 +2633,7 @@
         <v>2023</v>
       </c>
       <c r="E76" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -2653,7 +2650,7 @@
         <v>2023</v>
       </c>
       <c r="E77" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -2670,7 +2667,7 @@
         <v>2023</v>
       </c>
       <c r="E78" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -2687,7 +2684,7 @@
         <v>2023</v>
       </c>
       <c r="E79" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -2704,7 +2701,7 @@
         <v>2023</v>
       </c>
       <c r="E80" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -2721,7 +2718,7 @@
         <v>2023</v>
       </c>
       <c r="E81" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -2738,7 +2735,7 @@
         <v>2023</v>
       </c>
       <c r="E82" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -2755,7 +2752,7 @@
         <v>2023</v>
       </c>
       <c r="E83" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -2772,7 +2769,7 @@
         <v>2023</v>
       </c>
       <c r="E84" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -2789,7 +2786,7 @@
         <v>2023</v>
       </c>
       <c r="E85" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -2806,7 +2803,7 @@
         <v>2023</v>
       </c>
       <c r="E86" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2823,7 +2820,7 @@
         <v>2023</v>
       </c>
       <c r="E87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2840,7 +2837,7 @@
         <v>2023</v>
       </c>
       <c r="E88" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -2857,7 +2854,7 @@
         <v>2023</v>
       </c>
       <c r="E89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -2874,7 +2871,7 @@
         <v>2023</v>
       </c>
       <c r="E90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -2891,7 +2888,7 @@
         <v>2023</v>
       </c>
       <c r="E91" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -2908,7 +2905,7 @@
         <v>2023</v>
       </c>
       <c r="E92" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -2925,7 +2922,7 @@
         <v>2023</v>
       </c>
       <c r="E93" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -2936,13 +2933,13 @@
         <v>185</v>
       </c>
       <c r="C94" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D94">
         <v>2023</v>
       </c>
       <c r="E94" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -2953,13 +2950,13 @@
         <v>187</v>
       </c>
       <c r="C95" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D95">
         <v>2023</v>
       </c>
       <c r="E95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -2970,13 +2967,13 @@
         <v>189</v>
       </c>
       <c r="C96" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D96">
         <v>2023</v>
       </c>
       <c r="E96" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -2987,13 +2984,13 @@
         <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D97">
         <v>2023</v>
       </c>
       <c r="E97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -3004,13 +3001,13 @@
         <v>193</v>
       </c>
       <c r="C98" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D98">
         <v>2023</v>
       </c>
       <c r="E98" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -3021,13 +3018,13 @@
         <v>195</v>
       </c>
       <c r="C99" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D99">
         <v>2023</v>
       </c>
       <c r="E99" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -3038,13 +3035,13 @@
         <v>197</v>
       </c>
       <c r="C100" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D100">
         <v>2023</v>
       </c>
       <c r="E100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -3055,13 +3052,13 @@
         <v>199</v>
       </c>
       <c r="C101" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D101">
         <v>2023</v>
       </c>
       <c r="E101" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -3072,13 +3069,13 @@
         <v>201</v>
       </c>
       <c r="C102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D102">
         <v>2023</v>
       </c>
       <c r="E102" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -3089,13 +3086,13 @@
         <v>203</v>
       </c>
       <c r="C103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D103">
         <v>2023</v>
       </c>
       <c r="E103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -3106,13 +3103,13 @@
         <v>205</v>
       </c>
       <c r="C104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D104">
         <v>2023</v>
       </c>
       <c r="E104" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -3123,13 +3120,13 @@
         <v>207</v>
       </c>
       <c r="C105" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D105">
         <v>2023</v>
       </c>
       <c r="E105" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -3140,13 +3137,13 @@
         <v>209</v>
       </c>
       <c r="C106" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D106">
         <v>2023</v>
       </c>
       <c r="E106" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -3157,13 +3154,13 @@
         <v>211</v>
       </c>
       <c r="C107" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D107">
         <v>2023</v>
       </c>
       <c r="E107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -3174,13 +3171,13 @@
         <v>213</v>
       </c>
       <c r="C108" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D108">
         <v>2023</v>
       </c>
       <c r="E108" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -3191,13 +3188,13 @@
         <v>215</v>
       </c>
       <c r="C109" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D109">
         <v>2023</v>
       </c>
       <c r="E109" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -3208,13 +3205,13 @@
         <v>217</v>
       </c>
       <c r="C110" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D110">
         <v>2023</v>
       </c>
       <c r="E110" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -3225,13 +3222,13 @@
         <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D111">
         <v>2023</v>
       </c>
       <c r="E111" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -3242,13 +3239,13 @@
         <v>221</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D112">
         <v>2023</v>
       </c>
       <c r="E112" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -3265,7 +3262,7 @@
         <v>2023</v>
       </c>
       <c r="E113" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -3273,13 +3270,13 @@
         <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D114">
         <v>2008</v>
       </c>
       <c r="E114" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -3287,13 +3284,13 @@
         <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D115">
         <v>2008</v>
       </c>
       <c r="E115" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -3301,13 +3298,13 @@
         <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D116">
         <v>2008</v>
       </c>
       <c r="E116" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -3315,13 +3312,13 @@
         <v>227</v>
       </c>
       <c r="C117" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D117">
         <v>2008</v>
       </c>
       <c r="E117" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -3329,13 +3326,13 @@
         <v>228</v>
       </c>
       <c r="C118" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D118">
         <v>2008</v>
       </c>
       <c r="E118" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -3343,13 +3340,13 @@
         <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D119">
         <v>2008</v>
       </c>
       <c r="E119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -3363,7 +3360,7 @@
         <v>2017</v>
       </c>
       <c r="E120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -3377,7 +3374,7 @@
         <v>2018</v>
       </c>
       <c r="E121" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -3391,7 +3388,7 @@
         <v>2020</v>
       </c>
       <c r="E122" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -3405,7 +3402,7 @@
         <v>2020</v>
       </c>
       <c r="E123" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -3419,7 +3416,7 @@
         <v>2020</v>
       </c>
       <c r="E124" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -3433,7 +3430,7 @@
         <v>2020</v>
       </c>
       <c r="E125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -3447,7 +3444,7 @@
         <v>2020</v>
       </c>
       <c r="E126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -3461,7 +3458,7 @@
         <v>2020</v>
       </c>
       <c r="E127" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -3475,7 +3472,7 @@
         <v>2021</v>
       </c>
       <c r="E128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.2">
@@ -3489,7 +3486,7 @@
         <v>2021</v>
       </c>
       <c r="E129" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.2">
@@ -3503,7 +3500,7 @@
         <v>2021</v>
       </c>
       <c r="E130" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.2">
@@ -3517,7 +3514,7 @@
         <v>2021</v>
       </c>
       <c r="E131" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.2">
@@ -3531,7 +3528,7 @@
         <v>2021</v>
       </c>
       <c r="E132" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.2">
@@ -3545,7 +3542,7 @@
         <v>2021</v>
       </c>
       <c r="E133" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.2">
@@ -3559,7 +3556,7 @@
         <v>2021</v>
       </c>
       <c r="E134" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.2">
@@ -3573,7 +3570,7 @@
         <v>2021</v>
       </c>
       <c r="E135" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.2">
@@ -3587,7 +3584,7 @@
         <v>2021</v>
       </c>
       <c r="E136" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.2">
@@ -3601,7 +3598,7 @@
         <v>2021</v>
       </c>
       <c r="E137" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.2">
@@ -3615,7 +3612,7 @@
         <v>2021</v>
       </c>
       <c r="E138" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.2">
@@ -3629,7 +3626,7 @@
         <v>2021</v>
       </c>
       <c r="E139" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.2">
@@ -3643,7 +3640,7 @@
         <v>2021</v>
       </c>
       <c r="E140" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.2">
@@ -3657,7 +3654,7 @@
         <v>2021</v>
       </c>
       <c r="E141" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.2">
@@ -3671,7 +3668,7 @@
         <v>2021</v>
       </c>
       <c r="E142" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.2">
@@ -3685,7 +3682,7 @@
         <v>2021</v>
       </c>
       <c r="E143" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.2">
@@ -3699,7 +3696,7 @@
         <v>2021</v>
       </c>
       <c r="E144" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -3713,7 +3710,7 @@
         <v>2021</v>
       </c>
       <c r="E145" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -3727,7 +3724,7 @@
         <v>2021</v>
       </c>
       <c r="E146" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -3741,7 +3738,7 @@
         <v>2021</v>
       </c>
       <c r="E147" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -3755,7 +3752,7 @@
         <v>2021</v>
       </c>
       <c r="E148" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -3769,7 +3766,7 @@
         <v>2021</v>
       </c>
       <c r="E149" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -3777,13 +3774,13 @@
         <v>260</v>
       </c>
       <c r="C150" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D150">
         <v>1908</v>
       </c>
       <c r="E150" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3791,13 +3788,13 @@
         <v>261</v>
       </c>
       <c r="C151" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D151">
         <v>1930</v>
       </c>
       <c r="E151" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -3805,13 +3802,13 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D152">
         <v>1919</v>
       </c>
       <c r="E152" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -3819,13 +3816,13 @@
         <v>263</v>
       </c>
       <c r="C153" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D153">
         <v>1963</v>
       </c>
       <c r="E153" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3833,13 +3830,13 @@
         <v>264</v>
       </c>
       <c r="C154" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D154">
         <v>2000</v>
       </c>
       <c r="E154" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3847,251 +3844,251 @@
         <v>265</v>
       </c>
       <c r="C155" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D155">
         <v>2011</v>
       </c>
       <c r="E155" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B156" t="s">
         <v>266</v>
       </c>
       <c r="C156" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D156">
         <v>2018</v>
       </c>
       <c r="E156" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B157" t="s">
         <v>267</v>
       </c>
       <c r="C157" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D157">
         <v>2018</v>
       </c>
       <c r="E157" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B158" t="s">
         <v>268</v>
       </c>
       <c r="C158" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D158">
         <v>2018</v>
       </c>
       <c r="E158" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B159" t="s">
         <v>269</v>
       </c>
       <c r="C159" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D159">
         <v>2018</v>
       </c>
       <c r="E159" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B160" t="s">
         <v>270</v>
       </c>
       <c r="C160" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D160">
         <v>2018</v>
       </c>
       <c r="E160" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B161" t="s">
         <v>271</v>
       </c>
       <c r="C161" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D161">
         <v>2018</v>
       </c>
       <c r="E161" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B162" t="s">
         <v>272</v>
       </c>
       <c r="C162" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D162">
         <v>2018</v>
       </c>
       <c r="E162" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B163" t="s">
         <v>273</v>
       </c>
       <c r="C163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D163">
         <v>2018</v>
       </c>
       <c r="E163" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B164" t="s">
         <v>274</v>
       </c>
       <c r="C164" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D164">
         <v>2018</v>
       </c>
       <c r="E164" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B165" t="s">
         <v>275</v>
       </c>
       <c r="C165" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D165">
         <v>2018</v>
       </c>
       <c r="E165" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B166" t="s">
         <v>276</v>
       </c>
       <c r="C166" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D166">
         <v>2018</v>
       </c>
       <c r="E166" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B167" t="s">
         <v>277</v>
       </c>
       <c r="C167" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D167">
         <v>2018</v>
       </c>
       <c r="E167" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B168" t="s">
         <v>278</v>
       </c>
       <c r="C168" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D168">
         <v>2018</v>
       </c>
       <c r="E168" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B169" t="s">
         <v>279</v>
       </c>
       <c r="C169" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D169">
         <v>2018</v>
       </c>
       <c r="E169" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
+++ b/analyses/trees/RNA3/RNA3_SeqIDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdstengl/Google_Drive/Projects/Galbut_virus/Diverse_Collections/DiverseCollections/analyses/trees/RNA3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/trees/RNA3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78439F6-3983-2548-B757-B2F49E8EC239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE98457-C604-9649-96FE-E97289C308FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
+    <workbookView xWindow="34680" yWindow="500" windowWidth="28260" windowHeight="21100" xr2:uid="{6DFF8309-0216-3644-9CE5-EF91237D735A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="412">
   <si>
     <t>D_mel_USA_2020_mel-20-TD-3_Galbut_virus_RNA3_Complete_CDS_1</t>
   </si>
@@ -902,6 +902,9 @@
     <t>Ohio</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>Pennsylvania</t>
   </si>
   <si>
@@ -966,6 +969,309 @@
   </si>
   <si>
     <t>PV185894</t>
+  </si>
+  <si>
+    <t>sample_id</t>
+  </si>
+  <si>
+    <t>mel-21-MDS-9</t>
+  </si>
+  <si>
+    <t>500-F-11</t>
+  </si>
+  <si>
+    <t>500-F-21</t>
+  </si>
+  <si>
+    <t>500-F-67</t>
+  </si>
+  <si>
+    <t>500-M-16</t>
+  </si>
+  <si>
+    <t>500-M-17</t>
+  </si>
+  <si>
+    <t>500-M-54</t>
+  </si>
+  <si>
+    <t>500-M-57</t>
+  </si>
+  <si>
+    <t>500-M-61-2</t>
+  </si>
+  <si>
+    <t>500-M-61</t>
+  </si>
+  <si>
+    <t>500-M-65-2</t>
+  </si>
+  <si>
+    <t>500-M-65</t>
+  </si>
+  <si>
+    <t>500-M-71-2</t>
+  </si>
+  <si>
+    <t>500-M-83</t>
+  </si>
+  <si>
+    <t>500-M-84</t>
+  </si>
+  <si>
+    <t>500-M-F10</t>
+  </si>
+  <si>
+    <t>500-M-F11</t>
+  </si>
+  <si>
+    <t>500-M-G2</t>
+  </si>
+  <si>
+    <t>1020-B6</t>
+  </si>
+  <si>
+    <t>1020-C2</t>
+  </si>
+  <si>
+    <t>1020-D1</t>
+  </si>
+  <si>
+    <t>1020-D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1020-F1 </t>
+  </si>
+  <si>
+    <t>1020-F6</t>
+  </si>
+  <si>
+    <t>1020-F-31</t>
+  </si>
+  <si>
+    <t>1020-F-36</t>
+  </si>
+  <si>
+    <t>1020-F-44</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D4</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D11</t>
+  </si>
+  <si>
+    <t>1020-G3</t>
+  </si>
+  <si>
+    <t>1020-M-8</t>
+  </si>
+  <si>
+    <t>1020-M-19</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A5</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A7</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A10</t>
+  </si>
+  <si>
+    <t>1428-F-8</t>
+  </si>
+  <si>
+    <t>1428-F-21</t>
+  </si>
+  <si>
+    <t>1428-M-4</t>
+  </si>
+  <si>
+    <t>1428-M-6</t>
+  </si>
+  <si>
+    <t>1428-M-21</t>
+  </si>
+  <si>
+    <t>1428-M-42</t>
+  </si>
+  <si>
+    <t>Adobe-B4</t>
+  </si>
+  <si>
+    <t>Adobe-B6</t>
+  </si>
+  <si>
+    <t>Adobe-B8</t>
+  </si>
+  <si>
+    <t>Adobe-C2</t>
+  </si>
+  <si>
+    <t>Briarwood-D9</t>
+  </si>
+  <si>
+    <t>CVID-0825-B1</t>
+  </si>
+  <si>
+    <t>CVID-0825-C10</t>
+  </si>
+  <si>
+    <t>CVID-0911-F4</t>
+  </si>
+  <si>
+    <t>CVID-1006-G6</t>
+  </si>
+  <si>
+    <t>CVID-1006-G7</t>
+  </si>
+  <si>
+    <t>CVID-1006-H2</t>
+  </si>
+  <si>
+    <t>CVID-1006-H3</t>
+  </si>
+  <si>
+    <t>James-A4</t>
+  </si>
+  <si>
+    <t>James-A5</t>
+  </si>
+  <si>
+    <t>ME-F-1</t>
+  </si>
+  <si>
+    <t>ME-F-2</t>
+  </si>
+  <si>
+    <t>ME-F-3</t>
+  </si>
+  <si>
+    <t>ME-F-9</t>
+  </si>
+  <si>
+    <t>ME-M-1</t>
+  </si>
+  <si>
+    <t>ME-M-2</t>
+  </si>
+  <si>
+    <t>ME-M-4</t>
+  </si>
+  <si>
+    <t>ME-M-6</t>
+  </si>
+  <si>
+    <t>ME-M-10</t>
+  </si>
+  <si>
+    <t>ME-M-11</t>
+  </si>
+  <si>
+    <t>ME-M-14</t>
+  </si>
+  <si>
+    <t>ME-M-17</t>
+  </si>
+  <si>
+    <t>ME-M-18</t>
+  </si>
+  <si>
+    <t>ME-M-19</t>
+  </si>
+  <si>
+    <t>ME-M-20</t>
+  </si>
+  <si>
+    <t>Myrtle-D5</t>
+  </si>
+  <si>
+    <t>Myrtle-D11</t>
+  </si>
+  <si>
+    <t>Myrtle-E9</t>
+  </si>
+  <si>
+    <t>OH-M-5</t>
+  </si>
+  <si>
+    <t>Peach-8-F7</t>
+  </si>
+  <si>
+    <t>Peach-9-F8</t>
+  </si>
+  <si>
+    <t>Peach-10-F10</t>
+  </si>
+  <si>
+    <t>Penn-F-1</t>
+  </si>
+  <si>
+    <t>Penn-F-2</t>
+  </si>
+  <si>
+    <t>Penn-F-3</t>
+  </si>
+  <si>
+    <t>Penn-F-9</t>
+  </si>
+  <si>
+    <t>Penn-F-12</t>
+  </si>
+  <si>
+    <t>Penn-M-8</t>
+  </si>
+  <si>
+    <t>Penn-M-10</t>
+  </si>
+  <si>
+    <t>Penn-M-11</t>
+  </si>
+  <si>
+    <t>Penn-M-14</t>
+  </si>
+  <si>
+    <t>Penn-M-15</t>
+  </si>
+  <si>
+    <t>mel-20-TD-3</t>
+  </si>
+  <si>
+    <t>sim-20-TD-4</t>
+  </si>
+  <si>
+    <t>500-F-41</t>
+  </si>
+  <si>
+    <t>500-M-60</t>
+  </si>
+  <si>
+    <t>1020-A7</t>
+  </si>
+  <si>
+    <t>1020-F-40</t>
+  </si>
+  <si>
+    <t>1428-M-3</t>
+  </si>
+  <si>
+    <t>ME-M-7</t>
+  </si>
+  <si>
+    <t>ME-M-8</t>
+  </si>
+  <si>
+    <t>Peach-13-H7</t>
+  </si>
+  <si>
+    <t>Penn-F-4</t>
+  </si>
+  <si>
+    <t>Penn-M-2</t>
+  </si>
+  <si>
+    <t>ME-M-3</t>
   </si>
 </sst>
 </file>
@@ -1337,14 +1643,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DFA89E3-95EE-5B4C-BA29-97DEEB829153}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="63" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>280</v>
       </c>
@@ -1360,8 +1667,11 @@
       <c r="E1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1375,10 +1685,13 @@
         <v>2020</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1392,10 +1705,13 @@
         <v>2020</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1409,10 +1725,13 @@
         <v>2020</v>
       </c>
       <c r="E4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1426,10 +1745,13 @@
         <v>2020</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1443,10 +1765,13 @@
         <v>2021</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1460,10 +1785,13 @@
         <v>2023</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1477,10 +1805,13 @@
         <v>2023</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1494,10 +1825,13 @@
         <v>2023</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1511,10 +1845,13 @@
         <v>2023</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1528,10 +1865,13 @@
         <v>2023</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1545,10 +1885,13 @@
         <v>2023</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1562,10 +1905,13 @@
         <v>2023</v>
       </c>
       <c r="E13" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1579,10 +1925,13 @@
         <v>2023</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1596,10 +1945,13 @@
         <v>2023</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1613,10 +1965,13 @@
         <v>2023</v>
       </c>
       <c r="E16" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F16" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1630,10 +1985,13 @@
         <v>2023</v>
       </c>
       <c r="E17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1647,10 +2005,13 @@
         <v>2023</v>
       </c>
       <c r="E18" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F18" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1664,10 +2025,13 @@
         <v>2023</v>
       </c>
       <c r="E19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1681,10 +2045,13 @@
         <v>2023</v>
       </c>
       <c r="E20" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1698,10 +2065,13 @@
         <v>2023</v>
       </c>
       <c r="E21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1715,10 +2085,13 @@
         <v>2023</v>
       </c>
       <c r="E22" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -1732,10 +2105,13 @@
         <v>2023</v>
       </c>
       <c r="E23" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F23" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1749,10 +2125,13 @@
         <v>2023</v>
       </c>
       <c r="E24" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F24" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1766,10 +2145,13 @@
         <v>2023</v>
       </c>
       <c r="E25" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1783,10 +2165,13 @@
         <v>2023</v>
       </c>
       <c r="E26" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F26" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1800,10 +2185,13 @@
         <v>2023</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1817,10 +2205,13 @@
         <v>2023</v>
       </c>
       <c r="E28" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F28" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1834,10 +2225,13 @@
         <v>2023</v>
       </c>
       <c r="E29" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F29" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -1851,10 +2245,13 @@
         <v>2023</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F30" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1868,10 +2265,13 @@
         <v>2023</v>
       </c>
       <c r="E31" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F31" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1885,10 +2285,13 @@
         <v>2023</v>
       </c>
       <c r="E32" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F32" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1902,10 +2305,13 @@
         <v>2023</v>
       </c>
       <c r="E33" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F33" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -1919,10 +2325,13 @@
         <v>2023</v>
       </c>
       <c r="E34" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F34" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -1936,10 +2345,13 @@
         <v>2023</v>
       </c>
       <c r="E35" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F35" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1953,10 +2365,13 @@
         <v>2023</v>
       </c>
       <c r="E36" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F36" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -1970,10 +2385,13 @@
         <v>2023</v>
       </c>
       <c r="E37" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F37" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1987,10 +2405,13 @@
         <v>2023</v>
       </c>
       <c r="E38" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F38" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2004,10 +2425,13 @@
         <v>2023</v>
       </c>
       <c r="E39" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F39" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -2021,10 +2445,13 @@
         <v>2023</v>
       </c>
       <c r="E40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>78</v>
       </c>
@@ -2038,10 +2465,13 @@
         <v>2023</v>
       </c>
       <c r="E41" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F41" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2055,10 +2485,13 @@
         <v>2023</v>
       </c>
       <c r="E42" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F42" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2072,10 +2505,13 @@
         <v>2023</v>
       </c>
       <c r="E43" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -2089,10 +2525,13 @@
         <v>2023</v>
       </c>
       <c r="E44" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -2106,10 +2545,13 @@
         <v>2023</v>
       </c>
       <c r="E45" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F45" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -2123,10 +2565,13 @@
         <v>2023</v>
       </c>
       <c r="E46" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F46" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -2140,10 +2585,13 @@
         <v>2023</v>
       </c>
       <c r="E47" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -2157,10 +2605,13 @@
         <v>2023</v>
       </c>
       <c r="E48" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F48" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2174,10 +2625,13 @@
         <v>2023</v>
       </c>
       <c r="E49" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -2191,10 +2645,13 @@
         <v>2023</v>
       </c>
       <c r="E50" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F50" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -2208,10 +2665,13 @@
         <v>2023</v>
       </c>
       <c r="E51" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F51" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -2225,10 +2685,13 @@
         <v>2023</v>
       </c>
       <c r="E52" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F52" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -2242,10 +2705,13 @@
         <v>2023</v>
       </c>
       <c r="E53" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F53" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2259,10 +2725,13 @@
         <v>2023</v>
       </c>
       <c r="E54" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -2276,10 +2745,13 @@
         <v>2023</v>
       </c>
       <c r="E55" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2293,10 +2765,13 @@
         <v>2023</v>
       </c>
       <c r="E56" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F56" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2310,10 +2785,13 @@
         <v>2023</v>
       </c>
       <c r="E57" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -2327,10 +2805,13 @@
         <v>2023</v>
       </c>
       <c r="E58" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F58" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -2344,10 +2825,13 @@
         <v>2023</v>
       </c>
       <c r="E59" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F59" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2361,10 +2845,13 @@
         <v>2023</v>
       </c>
       <c r="E60" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F60" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2378,10 +2865,13 @@
         <v>2023</v>
       </c>
       <c r="E61" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>120</v>
       </c>
@@ -2395,10 +2885,13 @@
         <v>2023</v>
       </c>
       <c r="E62" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F62" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2412,10 +2905,13 @@
         <v>2023</v>
       </c>
       <c r="E63" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F63" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2429,10 +2925,13 @@
         <v>2023</v>
       </c>
       <c r="E64" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F64" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -2446,10 +2945,13 @@
         <v>2023</v>
       </c>
       <c r="E65" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F65" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -2463,10 +2965,13 @@
         <v>2023</v>
       </c>
       <c r="E66" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F66" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -2480,10 +2985,13 @@
         <v>2023</v>
       </c>
       <c r="E67" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F67" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -2497,10 +3005,13 @@
         <v>2023</v>
       </c>
       <c r="E68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F68" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -2514,10 +3025,13 @@
         <v>2023</v>
       </c>
       <c r="E69" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F69" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -2531,10 +3045,13 @@
         <v>2023</v>
       </c>
       <c r="E70" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F70" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>138</v>
       </c>
@@ -2548,10 +3065,13 @@
         <v>2023</v>
       </c>
       <c r="E71" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F71" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>140</v>
       </c>
@@ -2565,10 +3085,13 @@
         <v>2023</v>
       </c>
       <c r="E72" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F72" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -2582,10 +3105,13 @@
         <v>2023</v>
       </c>
       <c r="E73" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F73" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>144</v>
       </c>
@@ -2599,10 +3125,13 @@
         <v>2023</v>
       </c>
       <c r="E74" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F74" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>146</v>
       </c>
@@ -2616,10 +3145,13 @@
         <v>2023</v>
       </c>
       <c r="E75" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F75" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>148</v>
       </c>
@@ -2633,10 +3165,13 @@
         <v>2023</v>
       </c>
       <c r="E76" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F76" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>150</v>
       </c>
@@ -2650,10 +3185,13 @@
         <v>2023</v>
       </c>
       <c r="E77" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F77" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -2667,10 +3205,13 @@
         <v>2023</v>
       </c>
       <c r="E78" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F78" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2684,10 +3225,13 @@
         <v>2023</v>
       </c>
       <c r="E79" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F79" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>156</v>
       </c>
@@ -2701,10 +3245,13 @@
         <v>2023</v>
       </c>
       <c r="E80" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F80" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>158</v>
       </c>
@@ -2718,10 +3265,13 @@
         <v>2023</v>
       </c>
       <c r="E81" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F81" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>160</v>
       </c>
@@ -2735,10 +3285,13 @@
         <v>2023</v>
       </c>
       <c r="E82" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F82" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -2752,10 +3305,13 @@
         <v>2023</v>
       </c>
       <c r="E83" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F83" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -2769,10 +3325,13 @@
         <v>2023</v>
       </c>
       <c r="E84" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F84" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -2786,10 +3345,13 @@
         <v>2023</v>
       </c>
       <c r="E85" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F85" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2803,10 +3365,13 @@
         <v>2023</v>
       </c>
       <c r="E86" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -2820,10 +3385,13 @@
         <v>2023</v>
       </c>
       <c r="E87" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F87" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>172</v>
       </c>
@@ -2837,10 +3405,13 @@
         <v>2023</v>
       </c>
       <c r="E88" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F88" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>174</v>
       </c>
@@ -2854,10 +3425,13 @@
         <v>2023</v>
       </c>
       <c r="E89" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F89" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>176</v>
       </c>
@@ -2871,10 +3445,13 @@
         <v>2023</v>
       </c>
       <c r="E90" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F90" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -2888,10 +3465,13 @@
         <v>2023</v>
       </c>
       <c r="E91" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F91" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>180</v>
       </c>
@@ -2905,10 +3485,13 @@
         <v>2023</v>
       </c>
       <c r="E92" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F92" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>182</v>
       </c>
@@ -2922,10 +3505,13 @@
         <v>2023</v>
       </c>
       <c r="E93" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F93" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>184</v>
       </c>
@@ -2933,16 +3519,19 @@
         <v>185</v>
       </c>
       <c r="C94" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D94">
         <v>2023</v>
       </c>
       <c r="E94" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F94" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -2950,16 +3539,19 @@
         <v>187</v>
       </c>
       <c r="C95" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D95">
         <v>2023</v>
       </c>
       <c r="E95" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F95" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -2967,16 +3559,19 @@
         <v>189</v>
       </c>
       <c r="C96" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D96">
         <v>2023</v>
       </c>
       <c r="E96" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F96" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -2984,16 +3579,19 @@
         <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D97">
         <v>2023</v>
       </c>
       <c r="E97" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F97" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -3001,16 +3599,19 @@
         <v>193</v>
       </c>
       <c r="C98" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D98">
         <v>2023</v>
       </c>
       <c r="E98" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F98" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>194</v>
       </c>
@@ -3018,16 +3619,19 @@
         <v>195</v>
       </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D99">
         <v>2023</v>
       </c>
       <c r="E99" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F99" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>196</v>
       </c>
@@ -3035,16 +3639,19 @@
         <v>197</v>
       </c>
       <c r="C100" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D100">
         <v>2023</v>
       </c>
       <c r="E100" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F100" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>198</v>
       </c>
@@ -3052,16 +3659,19 @@
         <v>199</v>
       </c>
       <c r="C101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D101">
         <v>2023</v>
       </c>
       <c r="E101" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F101" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>200</v>
       </c>
@@ -3069,16 +3679,19 @@
         <v>201</v>
       </c>
       <c r="C102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D102">
         <v>2023</v>
       </c>
       <c r="E102" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F102" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>202</v>
       </c>
@@ -3086,16 +3699,19 @@
         <v>203</v>
       </c>
       <c r="C103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D103">
         <v>2023</v>
       </c>
       <c r="E103" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F103" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>204</v>
       </c>
@@ -3103,16 +3719,19 @@
         <v>205</v>
       </c>
       <c r="C104" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D104">
         <v>2023</v>
       </c>
       <c r="E104" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F104" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>206</v>
       </c>
@@ -3120,16 +3739,19 @@
         <v>207</v>
       </c>
       <c r="C105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D105">
         <v>2023</v>
       </c>
       <c r="E105" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F105" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>208</v>
       </c>
@@ -3137,16 +3759,19 @@
         <v>209</v>
       </c>
       <c r="C106" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D106">
         <v>2023</v>
       </c>
       <c r="E106" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F106" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -3154,16 +3779,19 @@
         <v>211</v>
       </c>
       <c r="C107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D107">
         <v>2023</v>
       </c>
       <c r="E107" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F107" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>212</v>
       </c>
@@ -3171,16 +3799,19 @@
         <v>213</v>
       </c>
       <c r="C108" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D108">
         <v>2023</v>
       </c>
       <c r="E108" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F108" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>214</v>
       </c>
@@ -3188,16 +3819,19 @@
         <v>215</v>
       </c>
       <c r="C109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D109">
         <v>2023</v>
       </c>
       <c r="E109" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F109" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>216</v>
       </c>
@@ -3205,16 +3839,19 @@
         <v>217</v>
       </c>
       <c r="C110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D110">
         <v>2023</v>
       </c>
       <c r="E110" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F110" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -3222,16 +3859,19 @@
         <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D111">
         <v>2023</v>
       </c>
       <c r="E111" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F111" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>220</v>
       </c>
@@ -3239,16 +3879,19 @@
         <v>221</v>
       </c>
       <c r="C112" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D112">
         <v>2023</v>
       </c>
       <c r="E112" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="F112" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>222</v>
       </c>
@@ -3262,94 +3905,97 @@
         <v>2023</v>
       </c>
       <c r="E113" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+      <c r="F113" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
         <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D114">
         <v>2008</v>
       </c>
       <c r="E114" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
         <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D115">
         <v>2008</v>
       </c>
       <c r="E115" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
         <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D116">
         <v>2008</v>
       </c>
       <c r="E116" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
         <v>227</v>
       </c>
       <c r="C117" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D117">
         <v>2008</v>
       </c>
       <c r="E117" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
         <v>228</v>
       </c>
       <c r="C118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D118">
         <v>2008</v>
       </c>
       <c r="E118" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
         <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D119">
         <v>2008</v>
       </c>
       <c r="E119" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
         <v>230</v>
       </c>
@@ -3360,10 +4006,10 @@
         <v>2017</v>
       </c>
       <c r="E120" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
         <v>231</v>
       </c>
@@ -3374,10 +4020,10 @@
         <v>2018</v>
       </c>
       <c r="E121" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
         <v>232</v>
       </c>
@@ -3388,10 +4034,10 @@
         <v>2020</v>
       </c>
       <c r="E122" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
         <v>233</v>
       </c>
@@ -3402,10 +4048,10 @@
         <v>2020</v>
       </c>
       <c r="E123" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
         <v>234</v>
       </c>
@@ -3416,10 +4062,10 @@
         <v>2020</v>
       </c>
       <c r="E124" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
         <v>235</v>
       </c>
@@ -3430,10 +4076,10 @@
         <v>2020</v>
       </c>
       <c r="E125" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
         <v>236</v>
       </c>
@@ -3444,10 +4090,10 @@
         <v>2020</v>
       </c>
       <c r="E126" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
         <v>237</v>
       </c>
@@ -3458,10 +4104,10 @@
         <v>2020</v>
       </c>
       <c r="E127" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
         <v>238</v>
       </c>
@@ -3472,7 +4118,7 @@
         <v>2021</v>
       </c>
       <c r="E128" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.2">
@@ -3486,7 +4132,7 @@
         <v>2021</v>
       </c>
       <c r="E129" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.2">
@@ -3500,7 +4146,7 @@
         <v>2021</v>
       </c>
       <c r="E130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.2">
@@ -3514,7 +4160,7 @@
         <v>2021</v>
       </c>
       <c r="E131" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.2">
@@ -3528,7 +4174,7 @@
         <v>2021</v>
       </c>
       <c r="E132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.2">
@@ -3542,7 +4188,7 @@
         <v>2021</v>
       </c>
       <c r="E133" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.2">
@@ -3556,7 +4202,7 @@
         <v>2021</v>
       </c>
       <c r="E134" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.2">
@@ -3570,7 +4216,7 @@
         <v>2021</v>
       </c>
       <c r="E135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.2">
@@ -3584,7 +4230,7 @@
         <v>2021</v>
       </c>
       <c r="E136" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.2">
@@ -3598,7 +4244,7 @@
         <v>2021</v>
       </c>
       <c r="E137" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.2">
@@ -3612,7 +4258,7 @@
         <v>2021</v>
       </c>
       <c r="E138" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.2">
@@ -3626,7 +4272,7 @@
         <v>2021</v>
       </c>
       <c r="E139" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.2">
@@ -3640,7 +4286,7 @@
         <v>2021</v>
       </c>
       <c r="E140" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.2">
@@ -3654,7 +4300,7 @@
         <v>2021</v>
       </c>
       <c r="E141" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.2">
@@ -3668,7 +4314,7 @@
         <v>2021</v>
       </c>
       <c r="E142" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.2">
@@ -3682,7 +4328,7 @@
         <v>2021</v>
       </c>
       <c r="E143" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.2">
@@ -3696,7 +4342,7 @@
         <v>2021</v>
       </c>
       <c r="E144" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -3710,7 +4356,7 @@
         <v>2021</v>
       </c>
       <c r="E145" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -3724,7 +4370,7 @@
         <v>2021</v>
       </c>
       <c r="E146" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -3738,7 +4384,7 @@
         <v>2021</v>
       </c>
       <c r="E147" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -3752,7 +4398,7 @@
         <v>2021</v>
       </c>
       <c r="E148" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -3766,7 +4412,7 @@
         <v>2021</v>
       </c>
       <c r="E149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -3774,13 +4420,13 @@
         <v>260</v>
       </c>
       <c r="C150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D150">
         <v>1908</v>
       </c>
       <c r="E150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3788,13 +4434,13 @@
         <v>261</v>
       </c>
       <c r="C151" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D151">
         <v>1930</v>
       </c>
       <c r="E151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -3802,13 +4448,13 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D152">
         <v>1919</v>
       </c>
       <c r="E152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -3816,13 +4462,13 @@
         <v>263</v>
       </c>
       <c r="C153" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D153">
         <v>1963</v>
       </c>
       <c r="E153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3830,13 +4476,13 @@
         <v>264</v>
       </c>
       <c r="C154" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D154">
         <v>2000</v>
       </c>
       <c r="E154" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3844,251 +4490,251 @@
         <v>265</v>
       </c>
       <c r="C155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D155">
         <v>2011</v>
       </c>
       <c r="E155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B156" t="s">
         <v>266</v>
       </c>
       <c r="C156" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D156">
         <v>2018</v>
       </c>
       <c r="E156" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B157" t="s">
         <v>267</v>
       </c>
       <c r="C157" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D157">
         <v>2018</v>
       </c>
       <c r="E157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B158" t="s">
         <v>268</v>
       </c>
       <c r="C158" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D158">
         <v>2018</v>
       </c>
       <c r="E158" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B159" t="s">
         <v>269</v>
       </c>
       <c r="C159" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D159">
         <v>2018</v>
       </c>
       <c r="E159" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B160" t="s">
         <v>270</v>
       </c>
       <c r="C160" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D160">
         <v>2018</v>
       </c>
       <c r="E160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B161" t="s">
         <v>271</v>
       </c>
       <c r="C161" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D161">
         <v>2018</v>
       </c>
       <c r="E161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B162" t="s">
         <v>272</v>
       </c>
       <c r="C162" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D162">
         <v>2018</v>
       </c>
       <c r="E162" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B163" t="s">
         <v>273</v>
       </c>
       <c r="C163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D163">
         <v>2018</v>
       </c>
       <c r="E163" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B164" t="s">
         <v>274</v>
       </c>
       <c r="C164" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D164">
         <v>2018</v>
       </c>
       <c r="E164" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B165" t="s">
         <v>275</v>
       </c>
       <c r="C165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D165">
         <v>2018</v>
       </c>
       <c r="E165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B166" t="s">
         <v>276</v>
       </c>
       <c r="C166" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D166">
         <v>2018</v>
       </c>
       <c r="E166" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B167" t="s">
         <v>277</v>
       </c>
       <c r="C167" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D167">
         <v>2018</v>
       </c>
       <c r="E167" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B168" t="s">
         <v>278</v>
       </c>
       <c r="C168" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D168">
         <v>2018</v>
       </c>
       <c r="E168" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B169" t="s">
         <v>279</v>
       </c>
       <c r="C169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D169">
         <v>2018</v>
       </c>
       <c r="E169" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
